--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717144</v>
+        <v>125718450</v>
       </c>
       <c r="B4" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498266</v>
+        <v>498097</v>
       </c>
       <c r="R4" t="n">
-        <v>6824499</v>
+        <v>6825031</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717883</v>
+        <v>125717144</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498158</v>
+        <v>498266</v>
       </c>
       <c r="R5" t="n">
-        <v>6824785</v>
+        <v>6824499</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125718450</v>
+        <v>125717883</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498097</v>
+        <v>498158</v>
       </c>
       <c r="R6" t="n">
-        <v>6825031</v>
+        <v>6824785</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R15" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,19 +2044,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R16" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2347,32 +2347,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719345</v>
+        <v>125718576</v>
       </c>
       <c r="B19" t="n">
-        <v>96577</v>
+        <v>98324</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497975</v>
+        <v>498024</v>
       </c>
       <c r="R19" t="n">
-        <v>6825193</v>
+        <v>6825148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
         <v>98324</v>
@@ -2472,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,54 +2550,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718921</v>
+        <v>125719345</v>
       </c>
       <c r="B21" t="n">
-        <v>98324</v>
+        <v>96577</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498031</v>
+        <v>497975</v>
       </c>
       <c r="R21" t="n">
-        <v>6825157</v>
+        <v>6825193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R2" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R3" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R15" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,19 +2044,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B16" t="n">
         <v>78967</v>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R16" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2347,32 +2347,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718576</v>
+        <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>98324</v>
+        <v>96584</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498024</v>
+        <v>497975</v>
       </c>
       <c r="R19" t="n">
-        <v>6825148</v>
+        <v>6825193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,26 +2472,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,45 +2541,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719345</v>
+        <v>125718921</v>
       </c>
       <c r="B21" t="n">
-        <v>96577</v>
+        <v>98331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497975</v>
+        <v>498031</v>
       </c>
       <c r="R21" t="n">
-        <v>6825193</v>
+        <v>6825157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R4" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B5" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R5" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125717883</v>
+        <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498158</v>
+        <v>498097</v>
       </c>
       <c r="R6" t="n">
-        <v>6824785</v>
+        <v>6825031</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -2153,10 +2153,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125719821</v>
+        <v>125719567</v>
       </c>
       <c r="B17" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497803</v>
+        <v>497901</v>
       </c>
       <c r="R17" t="n">
-        <v>6825327</v>
+        <v>6825280</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2238,22 +2238,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125719567</v>
+        <v>125719821</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497901</v>
+        <v>497803</v>
       </c>
       <c r="R18" t="n">
-        <v>6825280</v>
+        <v>6825327</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R2" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R3" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B4" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R4" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717883</v>
+        <v>125717144</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498158</v>
+        <v>498266</v>
       </c>
       <c r="R5" t="n">
-        <v>6824785</v>
+        <v>6824499</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,12 +1060,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125717763</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125717490</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>125718406</v>
       </c>
       <c r="B9" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125718273</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>125718275</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>125717602</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125719840</v>
       </c>
       <c r="B14" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>125717514</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125718153</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125719567</v>
+        <v>125719821</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2188,13 +2188,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>497901</v>
+        <v>497803</v>
       </c>
       <c r="R17" t="n">
-        <v>6825280</v>
+        <v>6825327</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2238,22 +2238,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125719821</v>
+        <v>125719567</v>
       </c>
       <c r="B18" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2261,21 +2261,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2285,13 +2285,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497803</v>
+        <v>497901</v>
       </c>
       <c r="R18" t="n">
-        <v>6825327</v>
+        <v>6825280</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2335,12 +2335,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2350,7 +2350,7 @@
         <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B21" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,26 +2578,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R21" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R2" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B3" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R3" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -881,7 +881,7 @@
         <v>125717883</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717144</v>
+        <v>125718450</v>
       </c>
       <c r="B5" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498266</v>
+        <v>498097</v>
       </c>
       <c r="R5" t="n">
-        <v>6824499</v>
+        <v>6825031</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B6" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R6" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
         <v>125717763</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125717490</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>125718406</v>
       </c>
       <c r="B9" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125718273</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>125718275</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>125717602</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125719840</v>
       </c>
       <c r="B14" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R15" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R16" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
         <v>125719821</v>
       </c>
       <c r="B17" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>125719567</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>125718921</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>125718576</v>
       </c>
       <c r="B21" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717883</v>
+        <v>125717144</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498158</v>
+        <v>498266</v>
       </c>
       <c r="R4" t="n">
-        <v>6824785</v>
+        <v>6824499</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125718450</v>
+        <v>125717883</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498097</v>
+        <v>498158</v>
       </c>
       <c r="R5" t="n">
-        <v>6825031</v>
+        <v>6824785</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125717144</v>
+        <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498266</v>
+        <v>498097</v>
       </c>
       <c r="R6" t="n">
-        <v>6824499</v>
+        <v>6825031</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2347,45 +2347,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719345</v>
+        <v>125718921</v>
       </c>
       <c r="B19" t="n">
-        <v>96591</v>
+        <v>98338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497975</v>
+        <v>498031</v>
       </c>
       <c r="R19" t="n">
-        <v>6825193</v>
+        <v>6825157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,7 +2453,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
         <v>98338</v>
@@ -2472,26 +2481,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718576</v>
+        <v>125719345</v>
       </c>
       <c r="B21" t="n">
-        <v>98338</v>
+        <v>96591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498024</v>
+        <v>497975</v>
       </c>
       <c r="R21" t="n">
-        <v>6825148</v>
+        <v>6825193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R2" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R3" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B15" t="n">
         <v>78972</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R15" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,19 +2044,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R16" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2347,10 +2347,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B19" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2375,26 +2375,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R19" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2553,7 +2553,7 @@
         <v>125719345</v>
       </c>
       <c r="B21" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R2" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B3" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R3" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717144</v>
+        <v>125718450</v>
       </c>
       <c r="B4" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498266</v>
+        <v>498097</v>
       </c>
       <c r="R4" t="n">
-        <v>6824499</v>
+        <v>6825031</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717883</v>
+        <v>125717144</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498158</v>
+        <v>498266</v>
       </c>
       <c r="R5" t="n">
-        <v>6824785</v>
+        <v>6824499</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125718450</v>
+        <v>125717883</v>
       </c>
       <c r="B6" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498097</v>
+        <v>498158</v>
       </c>
       <c r="R6" t="n">
-        <v>6825031</v>
+        <v>6824785</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R2" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>98341</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R3" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R4" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B5" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R5" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125717883</v>
+        <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,21 +1083,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498158</v>
+        <v>498097</v>
       </c>
       <c r="R6" t="n">
-        <v>6824785</v>
+        <v>6825031</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1172,7 +1172,7 @@
         <v>125717763</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125717490</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>125718406</v>
       </c>
       <c r="B9" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125718273</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>125718275</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>125717602</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125719840</v>
       </c>
       <c r="B14" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>125717514</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>125718153</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>125719821</v>
       </c>
       <c r="B17" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>125719567</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,32 +2347,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718576</v>
+        <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>96594</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2382,10 +2382,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498024</v>
+        <v>497975</v>
       </c>
       <c r="R19" t="n">
-        <v>6825148</v>
+        <v>6825193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,26 +2472,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,45 +2541,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719345</v>
+        <v>125718921</v>
       </c>
       <c r="B21" t="n">
-        <v>96592</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497975</v>
+        <v>498031</v>
       </c>
       <c r="R21" t="n">
-        <v>6825193</v>
+        <v>6825157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R2" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B3" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R3" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B4" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R4" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717883</v>
+        <v>125718450</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498158</v>
+        <v>498097</v>
       </c>
       <c r="R5" t="n">
-        <v>6824785</v>
+        <v>6825031</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R6" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,26 +2578,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R21" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R2" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R3" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R5" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125717144</v>
+        <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498266</v>
+        <v>498097</v>
       </c>
       <c r="R6" t="n">
-        <v>6824499</v>
+        <v>6825031</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2347,45 +2347,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719345</v>
+        <v>125718921</v>
       </c>
       <c r="B19" t="n">
-        <v>96596</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497975</v>
+        <v>498031</v>
       </c>
       <c r="R19" t="n">
-        <v>6825193</v>
+        <v>6825157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,10 +2453,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,26 +2481,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718576</v>
+        <v>125719345</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>96598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498024</v>
+        <v>497975</v>
       </c>
       <c r="R21" t="n">
-        <v>6825148</v>
+        <v>6825193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -1959,7 +1959,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R15" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,19 +2044,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R16" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2347,54 +2347,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125718921</v>
+        <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>96598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>498031</v>
+        <v>497975</v>
       </c>
       <c r="R19" t="n">
-        <v>6825157</v>
+        <v>6825193</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2453,7 +2444,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
         <v>98345</v>
@@ -2481,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125719345</v>
+        <v>125718576</v>
       </c>
       <c r="B21" t="n">
-        <v>96598</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>497975</v>
+        <v>498024</v>
       </c>
       <c r="R21" t="n">
-        <v>6825193</v>
+        <v>6825148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717883</v>
+        <v>125717144</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498158</v>
+        <v>498266</v>
       </c>
       <c r="R4" t="n">
-        <v>6824785</v>
+        <v>6824499</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B5" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R5" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1060,12 +1060,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1075,7 +1075,7 @@
         <v>125718450</v>
       </c>
       <c r="B6" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>125717763</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>125717490</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>125718406</v>
       </c>
       <c r="B9" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125718273</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>125718275</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>125717602</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>125719840</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125718153</v>
+        <v>125717514</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>498155</v>
+        <v>498303</v>
       </c>
       <c r="R15" t="n">
-        <v>6824869</v>
+        <v>6824763</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2044,22 +2044,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125717514</v>
+        <v>125718153</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>498303</v>
+        <v>498155</v>
       </c>
       <c r="R16" t="n">
-        <v>6824763</v>
+        <v>6824869</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2141,12 +2141,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
         <v>125719821</v>
       </c>
       <c r="B17" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2253,7 +2253,7 @@
         <v>125719567</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,26 +2472,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,10 +2541,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,17 +2569,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R21" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,45 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>98349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R2" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,54 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R3" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125719021</v>
       </c>
       <c r="B2" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125718751</v>
       </c>
       <c r="B10" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>125719345</v>
       </c>
       <c r="B19" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2444,10 +2444,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718576</v>
+        <v>125718921</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,17 +2472,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498024</v>
+        <v>498031</v>
       </c>
       <c r="R20" t="n">
-        <v>6825148</v>
+        <v>6825157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,10 +2550,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,26 +2578,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R21" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125719021</v>
+        <v>125719319</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>498030</v>
+        <v>497985</v>
       </c>
       <c r="R2" t="n">
-        <v>6825189</v>
+        <v>6825211</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -781,45 +772,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125719319</v>
+        <v>125719021</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497985</v>
+        <v>498030</v>
       </c>
       <c r="R3" t="n">
-        <v>6825211</v>
+        <v>6825189</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -878,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125717144</v>
+        <v>125717883</v>
       </c>
       <c r="B4" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kakolamm, Kakolamm, Dlr</t>
+          <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>498266</v>
+        <v>498158</v>
       </c>
       <c r="R4" t="n">
-        <v>6824499</v>
+        <v>6824785</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,22 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125717883</v>
+        <v>125718450</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -986,21 +986,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1010,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>498158</v>
+        <v>498097</v>
       </c>
       <c r="R5" t="n">
-        <v>6824785</v>
+        <v>6825031</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125718450</v>
+        <v>125717144</v>
       </c>
       <c r="B6" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,37 +1083,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kopparhålan, Kopparhålan, Dlr</t>
+          <t>Kakolamm, Kakolamm, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>498097</v>
+        <v>498266</v>
       </c>
       <c r="R6" t="n">
-        <v>6825031</v>
+        <v>6824499</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2347,45 +2347,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125719345</v>
+        <v>125718921</v>
       </c>
       <c r="B19" t="n">
-        <v>96605</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497975</v>
+        <v>498031</v>
       </c>
       <c r="R19" t="n">
-        <v>6825193</v>
+        <v>6825157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2444,7 +2453,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125718921</v>
+        <v>125718576</v>
       </c>
       <c r="B20" t="n">
         <v>98352</v>
@@ -2472,26 +2481,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kopparhålan, Kopparhålan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>498031</v>
+        <v>498024</v>
       </c>
       <c r="R20" t="n">
-        <v>6825157</v>
+        <v>6825148</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2550,32 +2550,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125718576</v>
+        <v>125719345</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>96605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>498024</v>
+        <v>497975</v>
       </c>
       <c r="R21" t="n">
-        <v>6825148</v>
+        <v>6825193</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 53785-2023 artfynd.xlsx
+++ b/artfynd/A 53785-2023 artfynd.xlsx
@@ -2650,7 +2650,7 @@
         <v>126808631</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>126808661</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
